--- a/Data/Search2_data.xlsx
+++ b/Data/Search2_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F78C388-B964-4556-B01C-69022B618838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7052F334-712F-4F07-A777-750EB4D870A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,16 +42,16 @@
     <t>áo</t>
   </si>
   <si>
-    <t>Có 189 kết quả tìm kiếm phù hợp</t>
-  </si>
-  <si>
     <t>q</t>
   </si>
   <si>
     <t>đen</t>
   </si>
   <si>
-    <t>CÓ 171 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+    <t>Có 224 kết quả tìm kiếm phù hợp</t>
+  </si>
+  <si>
+    <t>CÓ 201 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
   </si>
 </sst>
 </file>
@@ -389,12 +389,12 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
